--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6439111-765C-435B-953C-AFEAE084E164}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F26167-CE1F-4B80-B0B3-43A3797025F8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
   <sheets>
     <sheet name="MATRIZ" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="1451">
   <si>
     <t>TRADE</t>
   </si>
@@ -4375,6 +4375,27 @@
   </si>
   <si>
     <t>W07 SMU - UNIMARC PASCUA (PEDESTAL)</t>
+  </si>
+  <si>
+    <t>LT - MILO</t>
+  </si>
+  <si>
+    <t>W07 WALMART - LT MILO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>PIZARRAS SISA</t>
+  </si>
+  <si>
+    <t>30-02-2026</t>
+  </si>
+  <si>
+    <t>W08 SISA - CAMPAÑA PIZARRAS SISA</t>
+  </si>
+  <si>
+    <t>W09 JUMBO - CAMPAÑA AUDITORIA CREMA SIN LACTOSA (STOPPER)</t>
+  </si>
+  <si>
+    <t>W09 SISA - CAMPAÑA AUDITORIA CREMA SIN LACTOSA (STOPPER)</t>
   </si>
 </sst>
 </file>
@@ -4536,7 +4557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4603,9 +4624,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7812,10 +7830,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8136,18 +8150,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1349"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:H1353"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.42578125" customWidth="1"/>
-    <col min="9" max="9" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.44140625" customWidth="1"/>
+    <col min="9" max="9" width="47.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="48">
+    <row r="1" spans="1:8" ht="45.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -36296,7 +36310,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="1283" spans="1:8" ht="13.9" customHeight="1">
+    <row r="1283" spans="1:8" ht="13.95" customHeight="1">
       <c r="A1283" s="2" t="s">
         <v>12</v>
       </c>
@@ -37737,7 +37751,7 @@
       </c>
     </row>
     <row r="1339" spans="1:8">
-      <c r="A1339" s="24" t="s">
+      <c r="A1339" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1339" t="s">
@@ -37761,7 +37775,7 @@
       </c>
     </row>
     <row r="1340" spans="1:8">
-      <c r="A1340" s="24" t="s">
+      <c r="A1340" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1340" t="s">
@@ -37777,7 +37791,7 @@
         <v>46117</v>
       </c>
       <c r="G1340" s="8">
-        <f t="shared" ref="G1340:G1349" si="6">WORKDAY.INTL(F1340,10,1,0)+1</f>
+        <f t="shared" ref="G1340:G1352" si="6">WORKDAY.INTL(F1340,10,1,0)+1</f>
         <v>46130</v>
       </c>
       <c r="H1340" t="s">
@@ -37785,7 +37799,7 @@
       </c>
     </row>
     <row r="1341" spans="1:8">
-      <c r="A1341" s="24" t="s">
+      <c r="A1341" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1341" t="s">
@@ -37809,7 +37823,7 @@
       </c>
     </row>
     <row r="1342" spans="1:8">
-      <c r="A1342" s="24" t="s">
+      <c r="A1342" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1342" t="s">
@@ -37833,7 +37847,7 @@
       </c>
     </row>
     <row r="1343" spans="1:8">
-      <c r="A1343" s="24" t="s">
+      <c r="A1343" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1343" t="s">
@@ -37857,7 +37871,7 @@
       </c>
     </row>
     <row r="1344" spans="1:8">
-      <c r="A1344" s="24" t="s">
+      <c r="A1344" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1344" t="s">
@@ -37881,7 +37895,7 @@
       </c>
     </row>
     <row r="1345" spans="1:8">
-      <c r="A1345" s="24" t="s">
+      <c r="A1345" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1345" t="s">
@@ -37905,7 +37919,7 @@
       </c>
     </row>
     <row r="1346" spans="1:8">
-      <c r="A1346" s="24" t="s">
+      <c r="A1346" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1346" t="s">
@@ -37929,7 +37943,7 @@
       </c>
     </row>
     <row r="1347" spans="1:8">
-      <c r="A1347" s="24" t="s">
+      <c r="A1347" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1347" t="s">
@@ -37953,7 +37967,7 @@
       </c>
     </row>
     <row r="1348" spans="1:8">
-      <c r="A1348" s="24" t="s">
+      <c r="A1348" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1348" t="s">
@@ -37977,7 +37991,7 @@
       </c>
     </row>
     <row r="1349" spans="1:8">
-      <c r="A1349" s="24" t="s">
+      <c r="A1349" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B1349" t="s">
@@ -37998,6 +38012,105 @@
       </c>
       <c r="H1349" t="s">
         <v>1443</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:8">
+      <c r="A1350" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D1350" s="8">
+        <v>46064</v>
+      </c>
+      <c r="F1350" s="8">
+        <v>46134</v>
+      </c>
+      <c r="G1350" s="8">
+        <f t="shared" si="6"/>
+        <v>46149</v>
+      </c>
+      <c r="H1350" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:8">
+      <c r="A1351" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1351" s="8">
+        <v>46072</v>
+      </c>
+      <c r="E1351" s="23" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F1351" s="8">
+        <v>46104</v>
+      </c>
+      <c r="G1351" s="8">
+        <f t="shared" si="6"/>
+        <v>46119</v>
+      </c>
+      <c r="H1351" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:8">
+      <c r="A1352" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D1352" s="8">
+        <v>46076</v>
+      </c>
+      <c r="F1352" s="23">
+        <v>44987</v>
+      </c>
+      <c r="G1352" s="8">
+        <f t="shared" si="6"/>
+        <v>45002</v>
+      </c>
+      <c r="H1352" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:8">
+      <c r="A1353" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D1353" s="8">
+        <v>46076</v>
+      </c>
+      <c r="F1353" s="23">
+        <v>44987</v>
+      </c>
+      <c r="G1353" s="8">
+        <f t="shared" ref="G1353" si="7">WORKDAY.INTL(F1353,10,1,0)+1</f>
+        <v>45002</v>
+      </c>
+      <c r="H1353" t="s">
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
@@ -38009,7 +38122,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21B8E45-1E6E-4DBB-9B42-3C846D1884DC}">
   <dimension ref="A1:B775"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="16" t="s">

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F26167-CE1F-4B80-B0B3-43A3797025F8}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{166EADB1-1E6E-4629-9199-8B4460603839}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
   <sheets>
     <sheet name="MATRIZ" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="1462">
   <si>
     <t>TRADE</t>
   </si>
@@ -4396,6 +4396,39 @@
   </si>
   <si>
     <t>W09 SISA - CAMPAÑA AUDITORIA CREMA SIN LACTOSA (STOPPER)</t>
+  </si>
+  <si>
+    <t>W08 WALMART - PASCUA WM (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W08 WALMART - PASCUA WM (ISLA)</t>
+  </si>
+  <si>
+    <t>W08 JUMBO - PASCUA JUMBO (PEDESTAL)</t>
+  </si>
+  <si>
+    <t>W08 JUMBO - PASCUA JUMBO (CENEFA)</t>
+  </si>
+  <si>
+    <t>W08 JUMBO - PASCUA JUMBO (BOTADERO)</t>
+  </si>
+  <si>
+    <t>W08 SSRR - PASCUA SSRR (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W08 SSRR - PASCUA SSRR (ISLA)</t>
+  </si>
+  <si>
+    <t>W08 TOTTUS - PASCUA TOTTUS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W08 SISA - PASCUA SISA (PEDESTAL)</t>
+  </si>
+  <si>
+    <t>W08 SISA - PASCUA SISA (CENEFA)</t>
+  </si>
+  <si>
+    <t>W08 SISA - PASCUA SISA (BOTADERO)</t>
   </si>
 </sst>
 </file>
@@ -8150,18 +8183,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1353"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H1364"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.44140625" customWidth="1"/>
-    <col min="9" max="9" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.42578125" customWidth="1"/>
+    <col min="9" max="9" width="47.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45.6">
+    <row r="1" spans="1:8" ht="48">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -36310,7 +36343,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="1283" spans="1:8" ht="13.95" customHeight="1">
+    <row r="1283" spans="1:8" ht="13.9" customHeight="1">
       <c r="A1283" s="2" t="s">
         <v>12</v>
       </c>
@@ -38079,11 +38112,11 @@
         <v>46076</v>
       </c>
       <c r="F1352" s="23">
-        <v>44987</v>
+        <v>46083</v>
       </c>
       <c r="G1352" s="8">
         <f t="shared" si="6"/>
-        <v>45002</v>
+        <v>46098</v>
       </c>
       <c r="H1352" t="s">
         <v>1449</v>
@@ -38103,14 +38136,278 @@
         <v>46076</v>
       </c>
       <c r="F1353" s="23">
-        <v>44987</v>
+        <v>46083</v>
       </c>
       <c r="G1353" s="8">
-        <f t="shared" ref="G1353" si="7">WORKDAY.INTL(F1353,10,1,0)+1</f>
-        <v>45002</v>
+        <f t="shared" ref="G1353:G1364" si="7">WORKDAY.INTL(F1353,10,1,0)+1</f>
+        <v>46098</v>
       </c>
       <c r="H1353" t="s">
         <v>1450</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:8">
+      <c r="A1354" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1354" s="8">
+        <v>46093</v>
+      </c>
+      <c r="F1354" s="8">
+        <v>46117</v>
+      </c>
+      <c r="G1354" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1354" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:8">
+      <c r="A1355" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1355" s="8">
+        <v>46093</v>
+      </c>
+      <c r="F1355" s="8">
+        <v>46117</v>
+      </c>
+      <c r="G1355" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1355" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:8">
+      <c r="A1356" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1356" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1356" s="8">
+        <v>46097</v>
+      </c>
+      <c r="G1356" s="8">
+        <f t="shared" si="7"/>
+        <v>46112</v>
+      </c>
+      <c r="H1356" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:8">
+      <c r="A1357" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1357" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1357" s="8">
+        <v>46097</v>
+      </c>
+      <c r="G1357" s="8">
+        <f t="shared" si="7"/>
+        <v>46112</v>
+      </c>
+      <c r="H1357" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:8">
+      <c r="A1358" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1358" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1358" s="8">
+        <v>46097</v>
+      </c>
+      <c r="G1358" s="8">
+        <f t="shared" si="7"/>
+        <v>46112</v>
+      </c>
+      <c r="H1358" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:8">
+      <c r="A1359" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1359" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1359" s="8">
+        <v>46117</v>
+      </c>
+      <c r="G1359" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1359" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:8">
+      <c r="A1360" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1360" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1360" s="8">
+        <v>46117</v>
+      </c>
+      <c r="G1360" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1360" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:8">
+      <c r="A1361" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1361" s="8">
+        <v>46084</v>
+      </c>
+      <c r="F1361" s="8">
+        <v>46117</v>
+      </c>
+      <c r="G1361" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1361" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:8">
+      <c r="A1362" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1362" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1362" s="8">
+        <v>46116</v>
+      </c>
+      <c r="G1362" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1362" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:8">
+      <c r="A1363" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1363" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1363" s="8">
+        <v>46116</v>
+      </c>
+      <c r="G1363" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1363" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:8">
+      <c r="A1364" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D1364" s="8">
+        <v>46083</v>
+      </c>
+      <c r="F1364" s="8">
+        <v>46116</v>
+      </c>
+      <c r="G1364" s="8">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+      <c r="H1364" t="s">
+        <v>1461</v>
       </c>
     </row>
   </sheetData>
@@ -38122,7 +38419,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21B8E45-1E6E-4DBB-9B42-3C846D1884DC}">
   <dimension ref="A1:B775"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="16" t="s">

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{166EADB1-1E6E-4629-9199-8B4460603839}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE0C803-E9F2-430E-B6AD-BECE670C1AA0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
   <sheets>
     <sheet name="MATRIZ" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4874" uniqueCount="1476">
   <si>
     <t>TRADE</t>
   </si>
@@ -4389,9 +4387,6 @@
     <t>30-02-2026</t>
   </si>
   <si>
-    <t>W08 SISA - CAMPAÑA PIZARRAS SISA</t>
-  </si>
-  <si>
     <t>W09 JUMBO - CAMPAÑA AUDITORIA CREMA SIN LACTOSA (STOPPER)</t>
   </si>
   <si>
@@ -4429,13 +4424,58 @@
   </si>
   <si>
     <t>W08 SISA - PASCUA SISA (BOTADERO)</t>
+  </si>
+  <si>
+    <t>Paylaoders Campaña Fina Selección Tottus</t>
+  </si>
+  <si>
+    <t>W12 TOTTUS - CAMPAÑA FINA SELECCION (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W08 SISA - CAMPAÑA PIZARRAS SAVORY</t>
+  </si>
+  <si>
+    <t>W12 JUMBO - CAMPAÑA MUNDO TRENCITO (ISLA)</t>
+  </si>
+  <si>
+    <t>W12 SISA - CAMPAÑA MUNDO TRENCITO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W12 WALMART - LISTA DE TRAFICO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W12 SISA - EQUITY SAHNE NUSS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Tabletas KitKat</t>
+  </si>
+  <si>
+    <t>W12 JUMBO - TABLETAS KITKAT (ISLA)</t>
+  </si>
+  <si>
+    <t>Mundo Trencito</t>
+  </si>
+  <si>
+    <t>Lista de Trafico L1E3</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>Campaña Fina Selección</t>
+  </si>
+  <si>
+    <t>W14 WALMART - CAMPAÑA FINA SELECCION (REVESTIMIENTO PACK CABECERAS)</t>
+  </si>
+  <si>
+    <t>W14 WALMART - CAMPAÑA FINA SELECCION (CUBRE PALLETS)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4473,6 +4513,13 @@
       <color theme="1"/>
       <name val="HelveticaNeue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -4590,7 +4637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4657,6 +4704,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4678,9 +4734,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="TD PENDIENTE"/>
       <sheetName val="PANEL DE CONTROL"/>
@@ -7863,6 +7916,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8183,7 +8240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1364"/>
+  <dimension ref="A1:H1372"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -38095,7 +38152,7 @@
         <v>46119</v>
       </c>
       <c r="H1351" t="s">
-        <v>1448</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1352" spans="1:8">
@@ -38119,7 +38176,7 @@
         <v>46098</v>
       </c>
       <c r="H1352" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1353" spans="1:8">
@@ -38139,11 +38196,11 @@
         <v>46083</v>
       </c>
       <c r="G1353" s="8">
-        <f t="shared" ref="G1353:G1364" si="7">WORKDAY.INTL(F1353,10,1,0)+1</f>
+        <f t="shared" ref="G1353:G1366" si="7">WORKDAY.INTL(F1353,10,1,0)+1</f>
         <v>46098</v>
       </c>
       <c r="H1353" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1354" spans="1:8">
@@ -38167,7 +38224,7 @@
         <v>46130</v>
       </c>
       <c r="H1354" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1355" spans="1:8">
@@ -38191,7 +38248,7 @@
         <v>46130</v>
       </c>
       <c r="H1355" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1356" spans="1:8">
@@ -38215,7 +38272,7 @@
         <v>46112</v>
       </c>
       <c r="H1356" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1357" spans="1:8">
@@ -38239,7 +38296,7 @@
         <v>46112</v>
       </c>
       <c r="H1357" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1358" spans="1:8">
@@ -38263,7 +38320,7 @@
         <v>46112</v>
       </c>
       <c r="H1358" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1359" spans="1:8">
@@ -38287,7 +38344,7 @@
         <v>46130</v>
       </c>
       <c r="H1359" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1360" spans="1:8">
@@ -38311,7 +38368,7 @@
         <v>46130</v>
       </c>
       <c r="H1360" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1361" spans="1:8">
@@ -38335,7 +38392,7 @@
         <v>46130</v>
       </c>
       <c r="H1361" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1362" spans="1:8">
@@ -38359,7 +38416,7 @@
         <v>46130</v>
       </c>
       <c r="H1362" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1363" spans="1:8">
@@ -38383,7 +38440,7 @@
         <v>46130</v>
       </c>
       <c r="H1363" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1364" spans="1:8">
@@ -38407,7 +38464,223 @@
         <v>46130</v>
       </c>
       <c r="H1364" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:8">
+      <c r="A1365" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C1365" t="s">
         <v>1461</v>
+      </c>
+      <c r="D1365" s="25">
+        <v>46105</v>
+      </c>
+      <c r="E1365" s="25">
+        <v>46107</v>
+      </c>
+      <c r="F1365" s="21">
+        <v>46146</v>
+      </c>
+      <c r="G1365" s="24">
+        <f t="shared" si="7"/>
+        <v>46161</v>
+      </c>
+      <c r="H1365" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:8">
+      <c r="A1366" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1366" s="25">
+        <v>46105</v>
+      </c>
+      <c r="E1366" s="25">
+        <v>46105</v>
+      </c>
+      <c r="F1366" s="8">
+        <v>46139</v>
+      </c>
+      <c r="G1366" s="24">
+        <f t="shared" si="7"/>
+        <v>46154</v>
+      </c>
+      <c r="H1366" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:8">
+      <c r="A1367" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1367" s="25">
+        <v>46105</v>
+      </c>
+      <c r="E1367" s="25">
+        <v>46105</v>
+      </c>
+      <c r="F1367" s="8">
+        <v>46139</v>
+      </c>
+      <c r="G1367" s="24">
+        <f t="shared" ref="G1367:G1371" si="8">WORKDAY.INTL(F1367,10,1,0)+1</f>
+        <v>46154</v>
+      </c>
+      <c r="H1367" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:8">
+      <c r="A1368" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1368" s="26" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D1368" s="25">
+        <v>46107</v>
+      </c>
+      <c r="E1368" s="25">
+        <v>46107</v>
+      </c>
+      <c r="F1368" s="8">
+        <v>46134</v>
+      </c>
+      <c r="G1368" s="24">
+        <f t="shared" si="8"/>
+        <v>46149</v>
+      </c>
+      <c r="H1368" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:8">
+      <c r="A1369" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D1369" s="25">
+        <v>46105</v>
+      </c>
+      <c r="E1369" s="25">
+        <v>46105</v>
+      </c>
+      <c r="F1369" s="8">
+        <v>46139</v>
+      </c>
+      <c r="G1369" s="24">
+        <f t="shared" si="8"/>
+        <v>46154</v>
+      </c>
+      <c r="H1369" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:8">
+      <c r="A1370" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1370" s="25">
+        <v>46105</v>
+      </c>
+      <c r="E1370" s="25">
+        <v>46105</v>
+      </c>
+      <c r="F1370" s="8">
+        <v>46167</v>
+      </c>
+      <c r="G1370" s="24">
+        <f t="shared" si="8"/>
+        <v>46182</v>
+      </c>
+      <c r="H1370" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:8">
+      <c r="A1371" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D1371" s="25">
+        <v>46107</v>
+      </c>
+      <c r="E1371" s="25">
+        <v>46115</v>
+      </c>
+      <c r="F1371" s="8">
+        <v>46134</v>
+      </c>
+      <c r="G1371" s="24">
+        <f t="shared" si="8"/>
+        <v>46149</v>
+      </c>
+      <c r="H1371" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:8">
+      <c r="A1372" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D1372" s="25">
+        <v>46107</v>
+      </c>
+      <c r="E1372" s="25">
+        <v>46115</v>
+      </c>
+      <c r="F1372" s="8">
+        <v>46134</v>
+      </c>
+      <c r="G1372" s="24">
+        <f t="shared" ref="G1372" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
+        <v>46149</v>
+      </c>
+      <c r="H1372" t="s">
+        <v>1475</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE0C803-E9F2-430E-B6AD-BECE670C1AA0}"/>
+  <xr:revisionPtr revIDLastSave="359" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8CF67D0-B1BE-41C6-9C2C-045308AEB137}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4874" uniqueCount="1476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4898" uniqueCount="1484">
   <si>
     <t>TRADE</t>
   </si>
@@ -4469,6 +4469,30 @@
   </si>
   <si>
     <t>W14 WALMART - CAMPAÑA FINA SELECCION (CUBRE PALLETS)</t>
+  </si>
+  <si>
+    <t>W14 WALMART - MUNDO TRENCITO (REVESTIMIENTO CABECERA)</t>
+  </si>
+  <si>
+    <t>Corrida Milo</t>
+  </si>
+  <si>
+    <t>W14 WALMART - CORRIDA MILO (REVESTIMIENTO CABECERA)</t>
+  </si>
+  <si>
+    <t>W14 WALMART - CORRIDA MILO (CUBREPALLET)</t>
+  </si>
+  <si>
+    <t>W14 SISA - CAMPAÑA FINA SELECCION (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Dia de la Madre</t>
+  </si>
+  <si>
+    <t>W14 TOTTUS - DIA DE LA MADRE (ISLA)</t>
+  </si>
+  <si>
+    <t>W14 SMU - DIA DE LA MADRE (PAYLOADER)</t>
   </si>
 </sst>
 </file>
@@ -7916,10 +7940,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8240,7 +8260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1372"/>
+  <dimension ref="A1:H1378"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -38676,11 +38696,158 @@
         <v>46134</v>
       </c>
       <c r="G1372" s="24">
-        <f t="shared" ref="G1372" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
+        <f t="shared" ref="G1372:G1378" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
         <v>46149</v>
       </c>
       <c r="H1372" t="s">
         <v>1475</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:8">
+      <c r="A1373" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1373" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1373" s="8">
+        <v>46168</v>
+      </c>
+      <c r="G1373" s="24">
+        <f t="shared" si="9"/>
+        <v>46183</v>
+      </c>
+      <c r="H1373" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:8">
+      <c r="A1374" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1374" s="25">
+        <v>46130</v>
+      </c>
+      <c r="F1374" s="25">
+        <v>46132</v>
+      </c>
+      <c r="G1374" s="24">
+        <f t="shared" si="9"/>
+        <v>46147</v>
+      </c>
+      <c r="H1374" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:8">
+      <c r="A1375" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1375" s="25">
+        <v>46130</v>
+      </c>
+      <c r="F1375" s="25">
+        <v>46132</v>
+      </c>
+      <c r="G1375" s="24">
+        <f t="shared" si="9"/>
+        <v>46147</v>
+      </c>
+      <c r="H1375" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:8">
+      <c r="A1376" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D1376" s="25">
+        <v>46119</v>
+      </c>
+      <c r="E1376" s="25">
+        <v>46122</v>
+      </c>
+      <c r="F1376" s="25">
+        <v>46139</v>
+      </c>
+      <c r="G1376" s="24">
+        <f t="shared" si="9"/>
+        <v>46154</v>
+      </c>
+      <c r="H1376" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:8">
+      <c r="A1377" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1377" s="25">
+        <v>46127</v>
+      </c>
+      <c r="F1377" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1377" s="24">
+        <f t="shared" si="9"/>
+        <v>46165</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:8">
+      <c r="A1378" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1378" s="25">
+        <v>46125</v>
+      </c>
+      <c r="F1378" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1378" s="24">
+        <f t="shared" si="9"/>
+        <v>46165</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>1483</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="359" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8CF67D0-B1BE-41C6-9C2C-045308AEB137}"/>
+  <xr:revisionPtr revIDLastSave="369" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE03D97C-1889-42CF-B32A-6B66390EF20D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4898" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4902" uniqueCount="1485">
   <si>
     <t>TRADE</t>
   </si>
@@ -4493,6 +4493,9 @@
   </si>
   <si>
     <t>W14 SMU - DIA DE LA MADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W14 WALMART - DIA DE LA MADRE (PAYLOADER)</t>
   </si>
 </sst>
 </file>
@@ -8260,7 +8263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1378"/>
+  <dimension ref="A1:H1379"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -38696,7 +38699,7 @@
         <v>46134</v>
       </c>
       <c r="G1372" s="24">
-        <f t="shared" ref="G1372:G1378" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
+        <f t="shared" ref="G1372:G1379" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
         <v>46149</v>
       </c>
       <c r="H1372" t="s">
@@ -38848,6 +38851,30 @@
       </c>
       <c r="H1378" t="s">
         <v>1483</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:8">
+      <c r="A1379" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1379" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1379" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1379" s="24">
+        <f t="shared" si="9"/>
+        <v>46165</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>1484</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="369" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE03D97C-1889-42CF-B32A-6B66390EF20D}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123CAB9C-C6F2-488F-B0FA-B58A517E3B2E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4902" uniqueCount="1485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="1488">
   <si>
     <t>TRADE</t>
   </si>
@@ -4496,6 +4496,15 @@
   </si>
   <si>
     <t>W14 WALMART - DIA DE LA MADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W15 TOTTUS - TABLETAS KIT KAT (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W15 TOTTUS - TABLETAS KIT KAT (STOPPER)</t>
+  </si>
+  <si>
+    <t>W15 SMU - TABLETAS KIT KAT (PAYLOADER)</t>
   </si>
 </sst>
 </file>
@@ -8263,7 +8272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1379"/>
+  <dimension ref="A1:H1382"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -38699,7 +38708,7 @@
         <v>46134</v>
       </c>
       <c r="G1372" s="24">
-        <f t="shared" ref="G1372:G1379" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
+        <f t="shared" ref="G1372:G1382" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
         <v>46149</v>
       </c>
       <c r="H1372" t="s">
@@ -38875,6 +38884,81 @@
       </c>
       <c r="H1379" t="s">
         <v>1484</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:8">
+      <c r="A1380" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1380" s="25">
+        <v>46118</v>
+      </c>
+      <c r="F1380" s="25">
+        <v>46196</v>
+      </c>
+      <c r="G1380" s="24">
+        <f t="shared" si="9"/>
+        <v>46211</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:8">
+      <c r="A1381" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1381" s="25">
+        <v>46118</v>
+      </c>
+      <c r="F1381" s="25">
+        <v>46196</v>
+      </c>
+      <c r="G1381" s="24">
+        <f t="shared" si="9"/>
+        <v>46211</v>
+      </c>
+      <c r="H1381" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:8">
+      <c r="A1382" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1382" s="25">
+        <v>46127</v>
+      </c>
+      <c r="E1382" s="25">
+        <v>46134</v>
+      </c>
+      <c r="F1382" s="25">
+        <v>46154</v>
+      </c>
+      <c r="G1382" s="24">
+        <f t="shared" si="9"/>
+        <v>46169</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>1487</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123CAB9C-C6F2-488F-B0FA-B58A517E3B2E}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2577557-5EA2-4508-864E-35D9C2C0D8BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4914" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4934" uniqueCount="1494">
   <si>
     <t>TRADE</t>
   </si>
@@ -4505,6 +4505,24 @@
   </si>
   <si>
     <t>W15 SMU - TABLETAS KIT KAT (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Venta asistida</t>
+  </si>
+  <si>
+    <t>W16 TOTTUS - VENTA ASISTIDA (CANOA CHOCOLOVE)</t>
+  </si>
+  <si>
+    <t>W16 TOTTUS - VENTA ASISTIDA (CANOA CAPRI)</t>
+  </si>
+  <si>
+    <t>W14 SSRR - CORRIDA MILO (REVESTIMIENTO PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W14 SSRR - CORRIDA MILO (ESTRUCTURA PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W14 TOTTUS - CORRIDA MILO (ESTRUCTURA PAYLOADER MILO)</t>
   </si>
 </sst>
 </file>
@@ -8272,7 +8290,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1382"/>
+  <dimension ref="A1:H1387"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -38708,7 +38726,7 @@
         <v>46134</v>
       </c>
       <c r="G1372" s="24">
-        <f t="shared" ref="G1372:G1382" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
+        <f t="shared" ref="G1372:G1384" si="9">WORKDAY.INTL(F1372,10,1,0)+1</f>
         <v>46149</v>
       </c>
       <c r="H1372" t="s">
@@ -38959,6 +38977,126 @@
       </c>
       <c r="H1382" t="s">
         <v>1487</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:8">
+      <c r="A1383" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D1383" s="25">
+        <v>46128</v>
+      </c>
+      <c r="F1383" s="25">
+        <v>46142</v>
+      </c>
+      <c r="G1383" s="24">
+        <f t="shared" si="9"/>
+        <v>46157</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:8">
+      <c r="A1384" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D1384" s="25">
+        <v>46128</v>
+      </c>
+      <c r="F1384" s="25">
+        <v>46142</v>
+      </c>
+      <c r="G1384" s="24">
+        <f t="shared" si="9"/>
+        <v>46157</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:8">
+      <c r="A1385" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1385" s="25">
+        <v>46130</v>
+      </c>
+      <c r="F1385" s="25">
+        <v>46132</v>
+      </c>
+      <c r="G1385" s="24">
+        <f t="shared" ref="G1385:G1386" si="10">WORKDAY.INTL(F1385,10,1,0)+1</f>
+        <v>46147</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:8">
+      <c r="A1386" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1386" s="25">
+        <v>46130</v>
+      </c>
+      <c r="F1386" s="25">
+        <v>46132</v>
+      </c>
+      <c r="G1386" s="24">
+        <f t="shared" si="10"/>
+        <v>46147</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:8">
+      <c r="A1387" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1387" s="25">
+        <v>46130</v>
+      </c>
+      <c r="F1387" s="25">
+        <v>46132</v>
+      </c>
+      <c r="G1387" s="24">
+        <f t="shared" ref="G1387" si="11">WORKDAY.INTL(F1387,10,1,0)+1</f>
+        <v>46147</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>1493</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2577557-5EA2-4508-864E-35D9C2C0D8BA}"/>
+  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A312517A-210B-42E9-A318-04B3A001E5B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4934" uniqueCount="1494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4946" uniqueCount="1501">
   <si>
     <t>TRADE</t>
   </si>
@@ -4523,6 +4523,27 @@
   </si>
   <si>
     <t>W14 TOTTUS - CORRIDA MILO (ESTRUCTURA PAYLOADER MILO)</t>
+  </si>
+  <si>
+    <t>W16 WALMART - BODEGAZO ACUENTA (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W16 SSRR - DIA DE LA MADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W16 WALMART - AIR FRYER (GANCHERAS)</t>
+  </si>
+  <si>
+    <t>Bodegazo 2</t>
+  </si>
+  <si>
+    <t>Francisco Jordan</t>
+  </si>
+  <si>
+    <t>Culinarios</t>
+  </si>
+  <si>
+    <t>Air Fryer Walmart</t>
   </si>
 </sst>
 </file>
@@ -8290,7 +8311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1387"/>
+  <dimension ref="A1:H1390"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39092,11 +39113,83 @@
         <v>46132</v>
       </c>
       <c r="G1387" s="24">
-        <f t="shared" ref="G1387" si="11">WORKDAY.INTL(F1387,10,1,0)+1</f>
+        <f t="shared" ref="G1387:G1390" si="11">WORKDAY.INTL(F1387,10,1,0)+1</f>
         <v>46147</v>
       </c>
       <c r="H1387" t="s">
         <v>1493</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:8">
+      <c r="A1388" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D1388" s="25">
+        <v>46169</v>
+      </c>
+      <c r="F1388" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G1388" s="24">
+        <f t="shared" si="11"/>
+        <v>46268</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:8">
+      <c r="A1389" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1389" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1389" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1389" s="24">
+        <f t="shared" si="11"/>
+        <v>46165</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:8">
+      <c r="A1390" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D1390" s="25">
+        <v>46136</v>
+      </c>
+      <c r="F1390" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1390" s="24">
+        <f t="shared" si="11"/>
+        <v>46183</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>1496</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A312517A-210B-42E9-A318-04B3A001E5B1}"/>
+  <xr:revisionPtr revIDLastSave="486" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C0B367-A16A-4C3B-B232-03F4693753DE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4946" uniqueCount="1501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="1509">
   <si>
     <t>TRADE</t>
   </si>
@@ -4544,6 +4544,30 @@
   </si>
   <si>
     <t>Air Fryer Walmart</t>
+  </si>
+  <si>
+    <t>W17 WALMART - DIA DE LA MADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W17 ACUENTA - DIA DE LA MADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W17 SSRR - DIA DE LA MADRE (ISLA)</t>
+  </si>
+  <si>
+    <t>W17 JUMBO - DIA DE LA MADRE (ISLA)</t>
+  </si>
+  <si>
+    <t>Campaña Lacteos Culinarios</t>
+  </si>
+  <si>
+    <t>Lista de trafico - Capri</t>
+  </si>
+  <si>
+    <t>W17 WALMART - LISTA DE TRAFICO CAPRI (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W17 WALMART - LLCC (PAYLOADER)</t>
   </si>
 </sst>
 </file>
@@ -8311,7 +8335,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1390"/>
+  <dimension ref="A1:H1396"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39113,7 +39137,7 @@
         <v>46132</v>
       </c>
       <c r="G1387" s="24">
-        <f t="shared" ref="G1387:G1390" si="11">WORKDAY.INTL(F1387,10,1,0)+1</f>
+        <f t="shared" ref="G1387:G1393" si="11">WORKDAY.INTL(F1387,10,1,0)+1</f>
         <v>46147</v>
       </c>
       <c r="H1387" t="s">
@@ -39190,6 +39214,150 @@
       </c>
       <c r="H1390" t="s">
         <v>1496</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:8">
+      <c r="A1391" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1391" s="25">
+        <v>46136</v>
+      </c>
+      <c r="F1391" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1391" s="24">
+        <f t="shared" si="11"/>
+        <v>46165</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:8">
+      <c r="A1392" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1392" s="25">
+        <v>46136</v>
+      </c>
+      <c r="F1392" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1392" s="24">
+        <f t="shared" si="11"/>
+        <v>46165</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:8">
+      <c r="A1393" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1393" s="25">
+        <v>46136</v>
+      </c>
+      <c r="F1393" s="25">
+        <v>46152</v>
+      </c>
+      <c r="G1393" s="24">
+        <f t="shared" si="11"/>
+        <v>46165</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:8">
+      <c r="A1394" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D1394" s="25">
+        <v>46140</v>
+      </c>
+      <c r="F1394" s="25">
+        <v>46167</v>
+      </c>
+      <c r="G1394" s="24">
+        <f t="shared" ref="G1394:G1396" si="12">WORKDAY.INTL(F1394,10,1,0)+1</f>
+        <v>46182</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:8">
+      <c r="A1395" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1395" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1395" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1395" s="24">
+        <f t="shared" si="12"/>
+        <v>46183</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:8">
+      <c r="A1396" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D1396" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1396" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1396" s="24">
+        <f t="shared" si="12"/>
+        <v>46183</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>1507</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="486" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C0B367-A16A-4C3B-B232-03F4693753DE}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF00758-8250-4ACC-9368-83DFF8731A58}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="1522">
   <si>
     <t>TRADE</t>
   </si>
@@ -4568,6 +4568,45 @@
   </si>
   <si>
     <t>W17 WALMART - LLCC (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Caldos SISA</t>
+  </si>
+  <si>
+    <t>Air Fryer SISA</t>
+  </si>
+  <si>
+    <t>Air Fryer JUMBO</t>
+  </si>
+  <si>
+    <t>W18 SISA - CAMPAÑA CALDOS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W18 SISA - AIR FRYER (GANCHERAS)</t>
+  </si>
+  <si>
+    <t>W18 JUMBO - AIR FRYER (GANCHERAS)</t>
+  </si>
+  <si>
+    <t>W18 WALMART - CORRIDA MILO (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W18 WALMART - REPOSICION KIT KAT (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Reposicion Payloader Kit Kat</t>
+  </si>
+  <si>
+    <t>W18 SMU - CORRIDA MILO (PAYLOADER ANTIBRECHA)</t>
+  </si>
+  <si>
+    <t>W18 SISA - CORRIDA MILO (PAYLOADER ANTIBRECHA)</t>
+  </si>
+  <si>
+    <t>W19 TOTTUS - CALDOS TOTTUS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Caldos Tottus</t>
   </si>
 </sst>
 </file>
@@ -8015,6 +8054,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8335,7 +8378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1396"/>
+  <dimension ref="A1:H1404"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39305,7 +39348,7 @@
         <v>46167</v>
       </c>
       <c r="G1394" s="24">
-        <f t="shared" ref="G1394:G1396" si="12">WORKDAY.INTL(F1394,10,1,0)+1</f>
+        <f t="shared" ref="G1394:G1402" si="12">WORKDAY.INTL(F1394,10,1,0)+1</f>
         <v>46182</v>
       </c>
       <c r="H1394" t="s">
@@ -39358,6 +39401,198 @@
       </c>
       <c r="H1396" t="s">
         <v>1507</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:8">
+      <c r="A1397" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D1397" s="25">
+        <v>46141</v>
+      </c>
+      <c r="F1397" s="25">
+        <v>46172</v>
+      </c>
+      <c r="G1397" s="24">
+        <f t="shared" si="12"/>
+        <v>46186</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:8">
+      <c r="A1398" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D1398" s="25">
+        <v>46141</v>
+      </c>
+      <c r="F1398" s="25">
+        <v>46203</v>
+      </c>
+      <c r="G1398" s="24">
+        <f t="shared" si="12"/>
+        <v>46218</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:8">
+      <c r="A1399" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D1399" s="25">
+        <v>46141</v>
+      </c>
+      <c r="F1399" s="25">
+        <v>46203</v>
+      </c>
+      <c r="G1399" s="24">
+        <f t="shared" si="12"/>
+        <v>46218</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:8">
+      <c r="A1400" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1400" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1400" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1400" s="24">
+        <f t="shared" si="12"/>
+        <v>46183</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:8">
+      <c r="A1401" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D1401" s="25">
+        <v>46142</v>
+      </c>
+      <c r="F1401" s="25">
+        <v>46150</v>
+      </c>
+      <c r="G1401" s="24">
+        <f t="shared" si="12"/>
+        <v>46165</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:8">
+      <c r="A1402" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1402" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1402" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1402" s="24">
+        <f t="shared" si="12"/>
+        <v>46183</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:8">
+      <c r="A1403" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1403" s="25">
+        <v>46135</v>
+      </c>
+      <c r="F1403" s="25">
+        <v>46168</v>
+      </c>
+      <c r="G1403" s="24">
+        <f t="shared" ref="G1403:G1404" si="13">WORKDAY.INTL(F1403,10,1,0)+1</f>
+        <v>46183</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:8">
+      <c r="A1404" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D1404" s="25">
+        <v>46148</v>
+      </c>
+      <c r="F1404" s="25">
+        <v>46295</v>
+      </c>
+      <c r="G1404" s="24">
+        <f t="shared" si="13"/>
+        <v>46310</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>1520</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF00758-8250-4ACC-9368-83DFF8731A58}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{000FF64A-AC9A-4BC7-A452-C4100481E703}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1531">
   <si>
     <t>TRADE</t>
   </si>
@@ -4607,6 +4607,33 @@
   </si>
   <si>
     <t>Caldos Tottus</t>
+  </si>
+  <si>
+    <t>W20 SISA - AIRFRYER SISA (STOPPER)</t>
+  </si>
+  <si>
+    <t>W20 JUMBO - AIRFRYER JUMBO (STOPPER)</t>
+  </si>
+  <si>
+    <t>Mixes</t>
+  </si>
+  <si>
+    <t>W20 SMU - CAMPAÑA MIXES (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Nido</t>
+  </si>
+  <si>
+    <t>W21 SISA - CAMPAÑA NIDO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Mega</t>
+  </si>
+  <si>
+    <t>W21 WALMART - MEGA WM (CUBRECABECERA)</t>
+  </si>
+  <si>
+    <t>W21 WALMART - MEGA WM (HUINCHA)</t>
   </si>
 </sst>
 </file>
@@ -8378,7 +8405,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1404"/>
+  <dimension ref="A1:H1410"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39564,7 +39591,7 @@
         <v>46168</v>
       </c>
       <c r="G1403" s="24">
-        <f t="shared" ref="G1403:G1404" si="13">WORKDAY.INTL(F1403,10,1,0)+1</f>
+        <f t="shared" ref="G1403:G1409" si="13">WORKDAY.INTL(F1403,10,1,0)+1</f>
         <v>46183</v>
       </c>
       <c r="H1403" t="s">
@@ -39593,6 +39620,153 @@
       </c>
       <c r="H1404" t="s">
         <v>1520</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:8">
+      <c r="A1405" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D1405" s="25">
+        <v>46149</v>
+      </c>
+      <c r="F1405" s="25">
+        <v>46203</v>
+      </c>
+      <c r="G1405" s="24">
+        <f t="shared" si="13"/>
+        <v>46218</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:8">
+      <c r="A1406" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D1406" s="25">
+        <v>46149</v>
+      </c>
+      <c r="F1406" s="25">
+        <v>46203</v>
+      </c>
+      <c r="G1406" s="24">
+        <f t="shared" si="13"/>
+        <v>46218</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:8">
+      <c r="A1407" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D1407" s="25">
+        <v>46155</v>
+      </c>
+      <c r="E1407" s="25">
+        <v>46162</v>
+      </c>
+      <c r="F1407" s="25">
+        <v>46196</v>
+      </c>
+      <c r="G1407" s="24">
+        <f t="shared" si="13"/>
+        <v>46211</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:8">
+      <c r="A1408" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D1408" s="25">
+        <v>46168</v>
+      </c>
+      <c r="F1408" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G1408" s="24">
+        <f t="shared" si="13"/>
+        <v>46249</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:8">
+      <c r="A1409" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D1409" s="25">
+        <v>46169</v>
+      </c>
+      <c r="F1409" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1409" s="24">
+        <f t="shared" si="13"/>
+        <v>46240</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:8">
+      <c r="A1410" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D1410" s="25">
+        <v>46169</v>
+      </c>
+      <c r="F1410" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1410" s="24">
+        <f t="shared" ref="G1410" si="14">WORKDAY.INTL(F1410,10,1,0)+1</f>
+        <v>46240</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>1530</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{000FF64A-AC9A-4BC7-A452-C4100481E703}"/>
+  <xr:revisionPtr revIDLastSave="609" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FACF85C3-8316-4368-8FA4-176A8260F17B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="1537">
   <si>
     <t>TRADE</t>
   </si>
@@ -4634,6 +4634,24 @@
   </si>
   <si>
     <t>W21 WALMART - MEGA WM (HUINCHA)</t>
+  </si>
+  <si>
+    <t>W22 HIPER LIDER - MI SAZON (MINICABECERA)</t>
+  </si>
+  <si>
+    <t>W22 HIPER LIDER - TUCO (MINICABECERA)</t>
+  </si>
+  <si>
+    <t>W22 HIPER LIDER - CORRIDA MILO SANTIAGO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Onefood</t>
+  </si>
+  <si>
+    <t>Tuco / Mi Sazón</t>
+  </si>
+  <si>
+    <t>Corrida Milo Santiago</t>
   </si>
 </sst>
 </file>
@@ -8405,7 +8423,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1410"/>
+  <dimension ref="A1:H1413"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39762,11 +39780,92 @@
         <v>46225</v>
       </c>
       <c r="G1410" s="24">
-        <f t="shared" ref="G1410" si="14">WORKDAY.INTL(F1410,10,1,0)+1</f>
+        <f t="shared" ref="G1410:G1411" si="14">WORKDAY.INTL(F1410,10,1,0)+1</f>
         <v>46240</v>
       </c>
       <c r="H1410" t="s">
         <v>1530</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:8">
+      <c r="A1411" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1411" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1411" s="25">
+        <v>46178</v>
+      </c>
+      <c r="F1411" s="25">
+        <v>46195</v>
+      </c>
+      <c r="G1411" s="24">
+        <f t="shared" si="14"/>
+        <v>46210</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:8">
+      <c r="A1412" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1412" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1412" s="25">
+        <v>46178</v>
+      </c>
+      <c r="F1412" s="25">
+        <v>46195</v>
+      </c>
+      <c r="G1412" s="24">
+        <f t="shared" ref="G1412:G1413" si="15">WORKDAY.INTL(F1412,10,1,0)+1</f>
+        <v>46210</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:8">
+      <c r="A1413" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D1413" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1413" s="25">
+        <v>46176</v>
+      </c>
+      <c r="F1413" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1413" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>1533</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FACF85C3-8316-4368-8FA4-176A8260F17B}"/>
+  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{452D8848-0B83-435A-BEA1-15761AA45691}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5058" uniqueCount="1544">
   <si>
     <t>TRADE</t>
   </si>
@@ -4652,6 +4652,27 @@
   </si>
   <si>
     <t>Corrida Milo Santiago</t>
+  </si>
+  <si>
+    <t>W22 SMU - CORRIDA MILO SANTIAGO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W23 SISA - MUNDO TRENCITO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - TRAFICO KIT KAT &amp; SAHNENUSS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W23 JUMBO - MUNDO TRENCITO (ISLAS)</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - CAMPAÑA TRENCITO (HOTSPOT)</t>
+  </si>
+  <si>
+    <t>Tráfico KitKat y SN</t>
+  </si>
+  <si>
+    <t>Tráfico Trencito Galletas</t>
   </si>
 </sst>
 </file>
@@ -8423,7 +8444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1413"/>
+  <dimension ref="A1:H1418"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39834,7 +39855,7 @@
         <v>46195</v>
       </c>
       <c r="G1412" s="24">
-        <f t="shared" ref="G1412:G1413" si="15">WORKDAY.INTL(F1412,10,1,0)+1</f>
+        <f t="shared" ref="F1412:G1418" si="15">WORKDAY.INTL(F1412,10,1,0)+1</f>
         <v>46210</v>
       </c>
       <c r="H1412" t="s">
@@ -39866,6 +39887,141 @@
       </c>
       <c r="H1413" t="s">
         <v>1533</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:8">
+      <c r="A1414" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D1414" s="25">
+        <v>46155</v>
+      </c>
+      <c r="E1414" s="25">
+        <v>46176</v>
+      </c>
+      <c r="F1414" s="25">
+        <v>46195</v>
+      </c>
+      <c r="G1414" s="24">
+        <f t="shared" si="15"/>
+        <v>46210</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:8">
+      <c r="A1415" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1415" s="25">
+        <v>46168</v>
+      </c>
+      <c r="E1415" s="25">
+        <v>46185</v>
+      </c>
+      <c r="F1415" s="25">
+        <v>46195</v>
+      </c>
+      <c r="G1415" s="24">
+        <f t="shared" si="15"/>
+        <v>46210</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:8">
+      <c r="A1416" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1416" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1416" s="25">
+        <v>46190</v>
+      </c>
+      <c r="F1416" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1416" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:8">
+      <c r="A1417" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1417" s="25">
+        <v>46168</v>
+      </c>
+      <c r="E1417" s="25">
+        <v>46185</v>
+      </c>
+      <c r="F1417" s="25">
+        <v>46195</v>
+      </c>
+      <c r="G1417" s="24">
+        <f t="shared" si="15"/>
+        <v>46210</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:8">
+      <c r="A1418" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D1418" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1418" s="25">
+        <v>46190</v>
+      </c>
+      <c r="F1418" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1418" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>1541</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{452D8848-0B83-435A-BEA1-15761AA45691}"/>
+  <xr:revisionPtr revIDLastSave="719" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F4EE07-AB62-4A17-844A-F66546D82CAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5058" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5098" uniqueCount="1559">
   <si>
     <t>TRADE</t>
   </si>
@@ -4673,6 +4673,51 @@
   </si>
   <si>
     <t>Tráfico Trencito Galletas</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - CORRIDA MILO SANTIAGO (CUBREPALLET)</t>
+  </si>
+  <si>
+    <t>W23 LIDER EXPRESS - CORRIDA MILO SANTIAGO (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W23 ACUENTA - CORRIDA MILO SANTIAGO (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W23 LIDER EXPRESS - NATURNESS (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W23 LIDER EXPRESS - NATURNESS (STICKER)</t>
+  </si>
+  <si>
+    <t>Naturness</t>
+  </si>
+  <si>
+    <t>W23 UNIMARC - DISNEY SMU (VIBRIN CHUPON)</t>
+  </si>
+  <si>
+    <t>W23 UNIMARC - DISNEY SMU (BIG BOY)</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - HELADO KIT KAT (HUINCHA)</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - HELADO KIT KAT (VIBRIN CHUPON)</t>
+  </si>
+  <si>
+    <t>W23 HIPER LIDER - DIA DEL PADRE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Yogur Batido Nestlé</t>
+  </si>
+  <si>
+    <t>Disney</t>
+  </si>
+  <si>
+    <t>Trafico Kit Kat</t>
+  </si>
+  <si>
+    <t>Dia del papá</t>
   </si>
 </sst>
 </file>
@@ -8120,10 +8165,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8444,7 +8485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1418"/>
+  <dimension ref="A1:H1428"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -39855,7 +39896,7 @@
         <v>46195</v>
       </c>
       <c r="G1412" s="24">
-        <f t="shared" ref="F1412:G1418" si="15">WORKDAY.INTL(F1412,10,1,0)+1</f>
+        <f t="shared" ref="G1412:G1424" si="15">WORKDAY.INTL(F1412,10,1,0)+1</f>
         <v>46210</v>
       </c>
       <c r="H1412" t="s">
@@ -40022,6 +40063,276 @@
       </c>
       <c r="H1418" t="s">
         <v>1541</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:8">
+      <c r="A1419" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D1419" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1419" s="25">
+        <v>46176</v>
+      </c>
+      <c r="F1419" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1419" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1419" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:8">
+      <c r="A1420" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D1420" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1420" s="25">
+        <v>46176</v>
+      </c>
+      <c r="F1420" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1420" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1420" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:8">
+      <c r="A1421" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D1421" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1421" s="25">
+        <v>46176</v>
+      </c>
+      <c r="F1421" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1421" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:8">
+      <c r="A1422" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D1422" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1422" s="25">
+        <v>46185</v>
+      </c>
+      <c r="F1422" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1422" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1422" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:8">
+      <c r="A1423" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D1423" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1423" s="25">
+        <v>46185</v>
+      </c>
+      <c r="F1423" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1423" s="24">
+        <f t="shared" si="15"/>
+        <v>46240</v>
+      </c>
+      <c r="H1423" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:8">
+      <c r="A1424" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1424" s="25">
+        <v>46174</v>
+      </c>
+      <c r="E1424" s="25">
+        <v>46188</v>
+      </c>
+      <c r="F1424" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G1424" s="24">
+        <f t="shared" si="15"/>
+        <v>46268</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:8">
+      <c r="A1425" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1425" s="25">
+        <v>46174</v>
+      </c>
+      <c r="E1425" s="25">
+        <v>46188</v>
+      </c>
+      <c r="F1425" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G1425" s="24">
+        <f t="shared" ref="G1425:G1426" si="16">WORKDAY.INTL(F1425,10,1,0)+1</f>
+        <v>46268</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:8">
+      <c r="A1426" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D1426" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1426" s="25">
+        <v>46188</v>
+      </c>
+      <c r="F1426" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1426" s="24">
+        <f t="shared" si="16"/>
+        <v>46240</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:8">
+      <c r="A1427" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D1427" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1427" s="25">
+        <v>46188</v>
+      </c>
+      <c r="F1427" s="25">
+        <v>46225</v>
+      </c>
+      <c r="G1427" s="24">
+        <f t="shared" ref="G1427:G1428" si="17">WORKDAY.INTL(F1427,10,1,0)+1</f>
+        <v>46240</v>
+      </c>
+      <c r="H1427" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:8">
+      <c r="A1428" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D1428" s="25">
+        <v>46182</v>
+      </c>
+      <c r="E1428" s="25">
+        <v>46185</v>
+      </c>
+      <c r="F1428" s="25">
+        <v>46193</v>
+      </c>
+      <c r="G1428" s="24">
+        <f t="shared" si="17"/>
+        <v>46207</v>
+      </c>
+      <c r="H1428" t="s">
+        <v>1554</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="719" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F4EE07-AB62-4A17-844A-F66546D82CAB}"/>
+  <xr:revisionPtr revIDLastSave="730" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93320EED-2DB4-4229-A53E-257FCA4026E7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5098" uniqueCount="1559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="1561">
   <si>
     <t>TRADE</t>
   </si>
@@ -4718,6 +4718,12 @@
   </si>
   <si>
     <t>Dia del papá</t>
+  </si>
+  <si>
+    <t>W24 SSRR - DISNEY SSRR (STOPPER)</t>
+  </si>
+  <si>
+    <t>W24 SSRR - DISNEY SSRR (VIBRIN CHUPON)</t>
   </si>
 </sst>
 </file>
@@ -8485,7 +8491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1428"/>
+  <dimension ref="A1:H1430"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -40301,7 +40307,7 @@
         <v>46225</v>
       </c>
       <c r="G1427" s="24">
-        <f t="shared" ref="G1427:G1428" si="17">WORKDAY.INTL(F1427,10,1,0)+1</f>
+        <f t="shared" ref="G1427:G1430" si="17">WORKDAY.INTL(F1427,10,1,0)+1</f>
         <v>46240</v>
       </c>
       <c r="H1427" t="s">
@@ -40333,6 +40339,54 @@
       </c>
       <c r="H1428" t="s">
         <v>1554</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:8">
+      <c r="A1429" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1429" s="25">
+        <v>46175</v>
+      </c>
+      <c r="F1429" s="25">
+        <v>46252</v>
+      </c>
+      <c r="G1429" s="24">
+        <f t="shared" si="17"/>
+        <v>46267</v>
+      </c>
+      <c r="H1429" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:8">
+      <c r="A1430" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1430" s="25">
+        <v>46175</v>
+      </c>
+      <c r="F1430" s="25">
+        <v>46252</v>
+      </c>
+      <c r="G1430" s="24">
+        <f t="shared" si="17"/>
+        <v>46267</v>
+      </c>
+      <c r="H1430" t="s">
+        <v>1560</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="730" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93320EED-2DB4-4229-A53E-257FCA4026E7}"/>
+  <xr:revisionPtr revIDLastSave="777" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{986C5EDE-FB7B-43E3-BC4A-2F152C98DEE6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="1561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5126" uniqueCount="1571">
   <si>
     <t>TRADE</t>
   </si>
@@ -4724,6 +4724,36 @@
   </si>
   <si>
     <t>W24 SSRR - DISNEY SSRR (VIBRIN CHUPON)</t>
+  </si>
+  <si>
+    <t>Cafe</t>
+  </si>
+  <si>
+    <t>W25 ACUENTA - LCA (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Refrigerados</t>
+  </si>
+  <si>
+    <t>Magnesio</t>
+  </si>
+  <si>
+    <t>W25 JUMBO - MAGNESIO (STOPPER CON PISADO)</t>
+  </si>
+  <si>
+    <t>W25 JUMBO - MAGNESIO (STOPPER CON PINZA)</t>
+  </si>
+  <si>
+    <t>W25 UNIMARC - CALDOS SMU (PAYLOADER CALDOS)</t>
+  </si>
+  <si>
+    <t>Maggi</t>
+  </si>
+  <si>
+    <t>Caldos SMU</t>
+  </si>
+  <si>
+    <t>W25 HIPER LIDER - DISNEY WM (CUBRECABECERA)</t>
   </si>
 </sst>
 </file>
@@ -8171,6 +8201,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8491,7 +8525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H1430"/>
+  <dimension ref="A1:H1435"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -40307,7 +40341,7 @@
         <v>46225</v>
       </c>
       <c r="G1427" s="24">
-        <f t="shared" ref="G1427:G1430" si="17">WORKDAY.INTL(F1427,10,1,0)+1</f>
+        <f t="shared" ref="G1427:G1432" si="17">WORKDAY.INTL(F1427,10,1,0)+1</f>
         <v>46240</v>
       </c>
       <c r="H1427" t="s">
@@ -40387,6 +40421,141 @@
       </c>
       <c r="H1430" t="s">
         <v>1560</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:8">
+      <c r="A1431" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D1431" s="25">
+        <v>46155</v>
+      </c>
+      <c r="E1431" s="25">
+        <v>46162</v>
+      </c>
+      <c r="F1431" s="25">
+        <v>46196</v>
+      </c>
+      <c r="G1431" s="24">
+        <f t="shared" si="17"/>
+        <v>46211</v>
+      </c>
+      <c r="H1431" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:8">
+      <c r="A1432" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1432" s="25">
+        <v>46188</v>
+      </c>
+      <c r="E1432" s="25">
+        <v>46230</v>
+      </c>
+      <c r="F1432" s="25">
+        <v>46194</v>
+      </c>
+      <c r="G1432" s="24">
+        <f t="shared" si="17"/>
+        <v>46207</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:8">
+      <c r="A1433" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1433" s="25">
+        <v>46188</v>
+      </c>
+      <c r="E1433" s="25">
+        <v>46230</v>
+      </c>
+      <c r="F1433" s="25">
+        <v>46194</v>
+      </c>
+      <c r="G1433" s="24">
+        <f t="shared" ref="G1433:G1435" si="18">WORKDAY.INTL(F1433,10,1,0)+1</f>
+        <v>46207</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:8">
+      <c r="A1434" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D1434" s="25">
+        <v>46197</v>
+      </c>
+      <c r="E1434" s="25">
+        <v>46203</v>
+      </c>
+      <c r="F1434" s="25">
+        <v>46288</v>
+      </c>
+      <c r="G1434" s="24">
+        <f t="shared" si="18"/>
+        <v>46303</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:8">
+      <c r="A1435" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1435" s="25">
+        <v>46169</v>
+      </c>
+      <c r="E1435" s="25">
+        <v>46199</v>
+      </c>
+      <c r="F1435" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G1435" s="24">
+        <f t="shared" si="18"/>
+        <v>46268</v>
+      </c>
+      <c r="H1435" t="s">
+        <v>1570</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1042" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB7565A-9F99-481D-8507-DFB0FFB0A969}"/>
+  <xr:revisionPtr revIDLastSave="1073" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02490801-68DF-4135-9F25-BA666231564B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5488" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="1662">
   <si>
     <t>TRADE</t>
   </si>
@@ -5011,6 +5011,24 @@
   </si>
   <si>
     <t>W31 SMU - ESQUINERO LECHE CONDENSADA (ESQUINERO PALLET LLCC)</t>
+  </si>
+  <si>
+    <t>W31 UNIMARC - CALDOS SMU (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W31 SISA - CAMPAÑA MCKAY (GANCHERAS)</t>
+  </si>
+  <si>
+    <t>W31 SISA - CAMPAÑA MCKAY (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W31 JUMBO - CAMPAÑA MCKAY (GANCHERAS)</t>
+  </si>
+  <si>
+    <t>W31 JUMBO - CAMPAÑA MCKAY (HOTSPOT)</t>
+  </si>
+  <si>
+    <t>W31 JUMBO - CAMPAÑA MCKAY (REV. CABECERA)</t>
   </si>
 </sst>
 </file>
@@ -8823,7 +8841,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1" filterMode="1"/>
-  <dimension ref="A1:K1467"/>
+  <dimension ref="A1:K1473"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -43475,7 +43493,7 @@
         <v>46387</v>
       </c>
       <c r="G1461" s="24">
-        <f t="shared" ref="G1461:G1467" si="26">WORKDAY.INTL(F1461,10,1,0)+1</f>
+        <f t="shared" ref="G1461:G1473" si="26">WORKDAY.INTL(F1461,10,1,0)+1</f>
         <v>46402</v>
       </c>
       <c r="H1461" t="s">
@@ -43642,6 +43660,168 @@
       </c>
       <c r="H1467" t="s">
         <v>1655</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:8">
+      <c r="A1468" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1468" s="25">
+        <v>46239</v>
+      </c>
+      <c r="E1468" s="25">
+        <v>46248</v>
+      </c>
+      <c r="F1468" s="25">
+        <v>46287</v>
+      </c>
+      <c r="G1468" s="24">
+        <f t="shared" si="26"/>
+        <v>46302</v>
+      </c>
+      <c r="H1468" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:8">
+      <c r="A1469" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1469" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1469" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1469" s="25">
+        <v>46275</v>
+      </c>
+      <c r="G1469" s="24">
+        <f t="shared" si="26"/>
+        <v>46290</v>
+      </c>
+      <c r="H1469" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:8">
+      <c r="A1470" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1470" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1470" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1470" s="25">
+        <v>46275</v>
+      </c>
+      <c r="G1470" s="24">
+        <f t="shared" si="26"/>
+        <v>46290</v>
+      </c>
+      <c r="H1470" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:8">
+      <c r="A1471" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1471" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1471" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1471" s="25">
+        <v>46275</v>
+      </c>
+      <c r="G1471" s="24">
+        <f t="shared" si="26"/>
+        <v>46290</v>
+      </c>
+      <c r="H1471" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:8">
+      <c r="A1472" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1472" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1472" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1472" s="25">
+        <v>46275</v>
+      </c>
+      <c r="G1472" s="24">
+        <f t="shared" si="26"/>
+        <v>46290</v>
+      </c>
+      <c r="H1472" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:8">
+      <c r="A1473" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1473" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1473" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1473" s="25">
+        <v>46275</v>
+      </c>
+      <c r="G1473" s="24">
+        <f t="shared" si="26"/>
+        <v>46290</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>1661</v>
       </c>
     </row>
   </sheetData>

--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1073" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02490801-68DF-4135-9F25-BA666231564B}"/>
+  <xr:revisionPtr revIDLastSave="1128" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07D10D9-16DB-4324-8879-8494F5707F46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5548" uniqueCount="1675">
   <si>
     <t>TRADE</t>
   </si>
@@ -5029,6 +5029,45 @@
   </si>
   <si>
     <t>W31 JUMBO - CAMPAÑA MCKAY (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W32 SMU - CAMPAÑA MCKAY (ISLA)</t>
+  </si>
+  <si>
+    <t>W32 SMU - CAMPAÑA MCKAY (CUBREPALLET)</t>
+  </si>
+  <si>
+    <t>W32 SMU - CAMPAÑA MCKAY (VIBRIN)</t>
+  </si>
+  <si>
+    <t>W32 SMU - CAMPAÑA MCKAY (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W32 ACUENTA - CHILENIDAD ACUENTA (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W32 TOTTUS - MILO SABORIZANTES (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W32 LIDER EXPRESS - CHILENIDAD EXPRESS (REV. CABECERA)</t>
+  </si>
+  <si>
+    <t>W32 TOTTUS - CAMPAÑA MCKAY (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W32 TOTTUS - CAMPAÑA MCKAY (ARCO)</t>
+  </si>
+  <si>
+    <t>Chilenidad express</t>
+  </si>
+  <si>
+    <t>Chilenidad Acuenta</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>Milo Saborizantes y Lacteos</t>
   </si>
 </sst>
 </file>
@@ -8841,7 +8880,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1" filterMode="1"/>
-  <dimension ref="A1:K1473"/>
+  <dimension ref="A1:K1482"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -43493,7 +43532,7 @@
         <v>46387</v>
       </c>
       <c r="G1461" s="24">
-        <f t="shared" ref="G1461:G1473" si="26">WORKDAY.INTL(F1461,10,1,0)+1</f>
+        <f t="shared" ref="G1461:G1477" si="26">WORKDAY.INTL(F1461,10,1,0)+1</f>
         <v>46402</v>
       </c>
       <c r="H1461" t="s">
@@ -43822,6 +43861,249 @@
       </c>
       <c r="H1473" t="s">
         <v>1661</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:8">
+      <c r="A1474" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1474" s="25">
+        <v>46235</v>
+      </c>
+      <c r="E1474" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1474" s="25">
+        <v>46280</v>
+      </c>
+      <c r="G1474" s="24">
+        <f t="shared" si="26"/>
+        <v>46295</v>
+      </c>
+      <c r="H1474" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:8">
+      <c r="A1475" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1475" s="25">
+        <v>46235</v>
+      </c>
+      <c r="E1475" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1475" s="25">
+        <v>46280</v>
+      </c>
+      <c r="G1475" s="24">
+        <f t="shared" si="26"/>
+        <v>46295</v>
+      </c>
+      <c r="H1475" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:8">
+      <c r="A1476" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1476" s="25">
+        <v>46235</v>
+      </c>
+      <c r="E1476" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1476" s="25">
+        <v>46280</v>
+      </c>
+      <c r="G1476" s="24">
+        <f t="shared" si="26"/>
+        <v>46295</v>
+      </c>
+      <c r="H1476" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:8">
+      <c r="A1477" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1477" s="25">
+        <v>46235</v>
+      </c>
+      <c r="E1477" s="25">
+        <v>46251</v>
+      </c>
+      <c r="F1477" s="25">
+        <v>46280</v>
+      </c>
+      <c r="G1477" s="24">
+        <f t="shared" si="26"/>
+        <v>46295</v>
+      </c>
+      <c r="H1477" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:8">
+      <c r="A1478" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D1478" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1478" s="25">
+        <v>46269</v>
+      </c>
+      <c r="F1478" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1478" s="24">
+        <f t="shared" ref="G1478:G1482" si="27">WORKDAY.INTL(F1478,10,1,0)+1</f>
+        <v>46318</v>
+      </c>
+      <c r="H1478" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:8">
+      <c r="A1479" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D1479" s="25">
+        <v>46239</v>
+      </c>
+      <c r="E1479" s="25">
+        <v>46246</v>
+      </c>
+      <c r="F1479" s="25">
+        <v>46289</v>
+      </c>
+      <c r="G1479" s="24">
+        <f t="shared" si="27"/>
+        <v>46304</v>
+      </c>
+      <c r="H1479" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:8">
+      <c r="A1480" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D1480" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1480" s="25">
+        <v>46269</v>
+      </c>
+      <c r="F1480" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1480" s="24">
+        <f t="shared" si="27"/>
+        <v>46318</v>
+      </c>
+      <c r="H1480" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:8">
+      <c r="A1481" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1481" s="25">
+        <v>46231</v>
+      </c>
+      <c r="E1481" s="25">
+        <v>46241</v>
+      </c>
+      <c r="F1481" s="25">
+        <v>46258</v>
+      </c>
+      <c r="G1481" s="24">
+        <f t="shared" si="27"/>
+        <v>46273</v>
+      </c>
+      <c r="H1481" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:8">
+      <c r="A1482" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1482" s="25">
+        <v>46231</v>
+      </c>
+      <c r="E1482" s="25">
+        <v>46241</v>
+      </c>
+      <c r="F1482" s="25">
+        <v>46258</v>
+      </c>
+      <c r="G1482" s="24">
+        <f t="shared" si="27"/>
+        <v>46273</v>
+      </c>
+      <c r="H1482" t="s">
+        <v>1670</v>
       </c>
     </row>
   </sheetData>
